--- a/research/traditional_assets/database/data/india/india_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0491</v>
+        <v>-0.0594</v>
       </c>
       <c r="G2">
-        <v>-0.3429921259842519</v>
+        <v>-0.4176966150431317</v>
       </c>
       <c r="H2">
-        <v>-0.3429921259842519</v>
+        <v>-0.4176966150431317</v>
       </c>
       <c r="I2">
-        <v>-0.2611473565804274</v>
+        <v>-0.3671492710487817</v>
       </c>
       <c r="J2">
-        <v>-0.2611473565804274</v>
+        <v>-0.3671492710487817</v>
       </c>
       <c r="K2">
-        <v>-1058.7</v>
+        <v>-876</v>
       </c>
       <c r="L2">
-        <v>-0.476355455568054</v>
+        <v>-0.4419109115673712</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>135.8</v>
+        <v>465.5</v>
       </c>
       <c r="V2">
-        <v>2.788501026694045</v>
-      </c>
-      <c r="W2">
-        <v>1.36237292497748</v>
+        <v>0.1931615419726959</v>
       </c>
       <c r="X2">
-        <v>2.385183566006519</v>
-      </c>
-      <c r="Y2">
-        <v>-1.022810641029039</v>
+        <v>2.475401867181528</v>
       </c>
       <c r="Z2">
-        <v>1.095043358297201</v>
-      </c>
-      <c r="AA2">
-        <v>-0.285967678360268</v>
+        <v>2.022755102040816</v>
       </c>
       <c r="AB2">
-        <v>0.06367132873504991</v>
-      </c>
-      <c r="AC2">
-        <v>-0.3496390070953179</v>
+        <v>0.09987923818955714</v>
       </c>
       <c r="AD2">
-        <v>3648.7</v>
+        <v>3228.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3648.7</v>
+        <v>3228.4</v>
       </c>
       <c r="AG2">
-        <v>3512.9</v>
+        <v>2762.9</v>
       </c>
       <c r="AH2">
-        <v>0.9868285822469844</v>
+        <v>0.5725839348739868</v>
       </c>
       <c r="AI2">
-        <v>1.915227547110388</v>
+        <v>2.17752596789424</v>
       </c>
       <c r="AJ2">
-        <v>0.9863263701707098</v>
+        <v>0.5341207856480049</v>
       </c>
       <c r="AK2">
-        <v>1.985474481433335</v>
+        <v>2.716448726772196</v>
       </c>
       <c r="AL2">
-        <v>333.8</v>
+        <v>132.19</v>
       </c>
       <c r="AM2">
-        <v>333.8</v>
+        <v>119.49</v>
       </c>
       <c r="AN2">
-        <v>-6.37216206776109</v>
+        <v>-4.490749756572542</v>
       </c>
       <c r="AO2">
-        <v>-1.738765727980827</v>
+        <v>-5.505711475905893</v>
       </c>
       <c r="AP2">
-        <v>-6.13499825358016</v>
+        <v>-3.843232716650439</v>
       </c>
       <c r="AQ2">
-        <v>-1.738765727980827</v>
+        <v>-6.090886266633191</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +704,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0491</v>
+        <v>-0.0594</v>
       </c>
       <c r="G3">
-        <v>-0.3429921259842519</v>
+        <v>-0.4059947071683351</v>
       </c>
       <c r="H3">
-        <v>-0.3429921259842519</v>
+        <v>-0.4059947071683351</v>
       </c>
       <c r="I3">
-        <v>-0.2611473565804274</v>
+        <v>-0.3420780117362789</v>
       </c>
       <c r="J3">
-        <v>-0.2611473565804274</v>
+        <v>-0.3420780117362789</v>
       </c>
       <c r="K3">
-        <v>-1058.7</v>
+        <v>-764.3</v>
       </c>
       <c r="L3">
-        <v>-0.476355455568054</v>
+        <v>-0.4397077436428489</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +746,183 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>135.8</v>
+        <v>116</v>
       </c>
       <c r="V3">
-        <v>2.788501026694045</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="W3">
-        <v>1.36237292497748</v>
+        <v>0.4145243518819828</v>
       </c>
       <c r="X3">
-        <v>2.385183566006519</v>
+        <v>4.852112910879915</v>
       </c>
       <c r="Y3">
-        <v>-1.022810641029039</v>
+        <v>-4.437588558997932</v>
       </c>
       <c r="Z3">
-        <v>1.095043358297201</v>
+        <v>1.773673469387755</v>
       </c>
       <c r="AA3">
-        <v>-0.285967678360268</v>
+        <v>-0.6067346938775511</v>
       </c>
       <c r="AB3">
-        <v>0.06367132873504991</v>
+        <v>0.1015414913769352</v>
       </c>
       <c r="AC3">
-        <v>-0.3496390070953179</v>
+        <v>-0.7082761852544863</v>
       </c>
       <c r="AD3">
-        <v>3648.7</v>
+        <v>3200.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3648.7</v>
+        <v>3200.8</v>
       </c>
       <c r="AG3">
-        <v>3512.9</v>
+        <v>3084.8</v>
       </c>
       <c r="AH3">
-        <v>0.9868285822469844</v>
+        <v>0.9913280475718533</v>
       </c>
       <c r="AI3">
-        <v>1.915227547110388</v>
+        <v>4.033774417139257</v>
       </c>
       <c r="AJ3">
-        <v>0.9863263701707098</v>
+        <v>0.9910048830634798</v>
       </c>
       <c r="AK3">
-        <v>1.985474481433335</v>
+        <v>4.553210332103322</v>
       </c>
       <c r="AL3">
-        <v>333.8</v>
+        <v>130.1</v>
       </c>
       <c r="AM3">
-        <v>333.8</v>
+        <v>130.1</v>
       </c>
       <c r="AN3">
-        <v>-6.37216206776109</v>
+        <v>-5.435218203430124</v>
       </c>
       <c r="AO3">
-        <v>-1.738765727980827</v>
+        <v>-4.570330514988471</v>
       </c>
       <c r="AP3">
-        <v>-6.13499825358016</v>
+        <v>-5.238240787909662</v>
       </c>
       <c r="AQ3">
-        <v>-1.738765727980827</v>
+        <v>-4.570330514988471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PB Fintech Limited (NSEI:POLICYBZR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.5010241704219582</v>
+      </c>
+      <c r="H4">
+        <v>-0.5010241704219582</v>
+      </c>
+      <c r="I4">
+        <v>-0.5456780008193363</v>
+      </c>
+      <c r="J4">
+        <v>-0.5456780008193363</v>
+      </c>
+      <c r="K4">
+        <v>-111.7</v>
+      </c>
+      <c r="L4">
+        <v>-0.45759934453093</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>349.5</v>
+      </c>
+      <c r="V4">
+        <v>0.1467316008228725</v>
+      </c>
+      <c r="X4">
+        <v>0.09869082348314101</v>
+      </c>
+      <c r="AB4">
+        <v>0.09821698500217906</v>
+      </c>
+      <c r="AD4">
+        <v>27.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>27.6</v>
+      </c>
+      <c r="AG4">
+        <v>-321.9</v>
+      </c>
+      <c r="AH4">
+        <v>0.01145465864287197</v>
+      </c>
+      <c r="AI4">
+        <v>0.04005224205485416</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1562621359223301</v>
+      </c>
+      <c r="AK4">
+        <v>-0.9478798586572437</v>
+      </c>
+      <c r="AL4">
+        <v>2.09</v>
+      </c>
+      <c r="AM4">
+        <v>-10.61</v>
+      </c>
+      <c r="AN4">
+        <v>-0.2123076923076923</v>
+      </c>
+      <c r="AO4">
+        <v>-63.73205741626794</v>
+      </c>
+      <c r="AP4">
+        <v>2.476153846153846</v>
+      </c>
+      <c r="AQ4">
+        <v>12.55419415645617</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_general.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0594</v>
+        <v>-0.0299</v>
       </c>
       <c r="G2">
-        <v>-0.4176966150431317</v>
+        <v>-0.1013998782714546</v>
       </c>
       <c r="H2">
-        <v>-0.4176966150431317</v>
+        <v>-0.1013998782714546</v>
       </c>
       <c r="I2">
-        <v>-0.3671492710487817</v>
+        <v>-0.0858997768310002</v>
       </c>
       <c r="J2">
-        <v>-0.3671492710487817</v>
+        <v>-0.0858997768310002</v>
       </c>
       <c r="K2">
-        <v>-876</v>
+        <v>-180.5</v>
       </c>
       <c r="L2">
-        <v>-0.4419109115673712</v>
+        <v>-0.07324000811523636</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,61 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>465.5</v>
+        <v>178.1</v>
       </c>
       <c r="V2">
-        <v>0.1931615419726959</v>
+        <v>0.0410378119311505</v>
+      </c>
+      <c r="W2">
+        <v>0.0212695153985539</v>
       </c>
       <c r="X2">
-        <v>2.475401867181528</v>
+        <v>1.078379107584357</v>
+      </c>
+      <c r="Y2">
+        <v>-1.057109592185803</v>
       </c>
       <c r="Z2">
-        <v>2.022755102040816</v>
+        <v>7.381615598885793</v>
       </c>
       <c r="AB2">
-        <v>0.09987923818955714</v>
+        <v>0.08693088361777873</v>
       </c>
       <c r="AD2">
-        <v>3228.4</v>
+        <v>2150.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3228.4</v>
+        <v>2150.1</v>
       </c>
       <c r="AG2">
-        <v>2762.9</v>
+        <v>1972</v>
       </c>
       <c r="AH2">
-        <v>0.5725839348739868</v>
+        <v>0.3312942989214175</v>
       </c>
       <c r="AI2">
-        <v>2.17752596789424</v>
+        <v>1.378180885840651</v>
       </c>
       <c r="AJ2">
-        <v>0.5341207856480049</v>
+        <v>0.3124257355154549</v>
       </c>
       <c r="AK2">
-        <v>2.716448726772196</v>
+        <v>1.426917510853835</v>
       </c>
       <c r="AL2">
-        <v>132.19</v>
+        <v>3.03</v>
       </c>
       <c r="AM2">
-        <v>119.49</v>
+        <v>-23.609</v>
       </c>
       <c r="AN2">
-        <v>-4.490749756572542</v>
+        <v>-10.56560196560197</v>
       </c>
       <c r="AO2">
-        <v>-5.505711475905893</v>
+        <v>-69.86798679867987</v>
       </c>
       <c r="AP2">
-        <v>-3.843232716650439</v>
+        <v>-9.690417690417691</v>
       </c>
       <c r="AQ2">
-        <v>-6.090886266633191</v>
+        <v>8.966919395145919</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reliance Capital Limited (NSEI:RELCAPITAL)</t>
+          <t>PB Fintech Limited (NSEI:POLICYBZR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -703,26 +709,23 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0594</v>
-      </c>
       <c r="G3">
-        <v>-0.4059947071683351</v>
+        <v>-0.2397414277684092</v>
       </c>
       <c r="H3">
-        <v>-0.4059947071683351</v>
+        <v>-0.2397414277684092</v>
       </c>
       <c r="I3">
-        <v>-0.3420780117362789</v>
+        <v>-0.1503653738055087</v>
       </c>
       <c r="J3">
-        <v>-0.3420780117362789</v>
+        <v>-0.1503653738055087</v>
       </c>
       <c r="K3">
-        <v>-764.3</v>
+        <v>-15.4</v>
       </c>
       <c r="L3">
-        <v>-0.4397077436428489</v>
+        <v>-0.04328274311410905</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,73 +749,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>116</v>
+        <v>64.7</v>
       </c>
       <c r="V3">
-        <v>4.142857142857143</v>
+        <v>0.01503427442779133</v>
       </c>
       <c r="W3">
-        <v>0.4145243518819828</v>
+        <v>-0.02331920048455482</v>
       </c>
       <c r="X3">
-        <v>4.852112910879915</v>
+        <v>0.08769335577338311</v>
       </c>
       <c r="Y3">
-        <v>-4.437588558997932</v>
+        <v>-0.1110125562579379</v>
       </c>
       <c r="Z3">
-        <v>1.773673469387755</v>
+        <v>1.06568424836014</v>
       </c>
       <c r="AA3">
-        <v>-0.6067346938775511</v>
+        <v>-0.1602420103633151</v>
       </c>
       <c r="AB3">
-        <v>0.1015414913769352</v>
+        <v>0.08743498667493513</v>
       </c>
       <c r="AC3">
-        <v>-0.7082761852544863</v>
+        <v>-0.2476769970382502</v>
       </c>
       <c r="AD3">
-        <v>3200.8</v>
+        <v>31.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3200.8</v>
+        <v>31.7</v>
       </c>
       <c r="AG3">
-        <v>3084.8</v>
+        <v>-33</v>
       </c>
       <c r="AH3">
-        <v>0.9913280475718533</v>
+        <v>0.007312234729654918</v>
       </c>
       <c r="AI3">
-        <v>4.033774417139257</v>
+        <v>0.04451621963207415</v>
       </c>
       <c r="AJ3">
-        <v>0.9910048830634798</v>
+        <v>-0.007727432384966632</v>
       </c>
       <c r="AK3">
-        <v>4.553210332103322</v>
+        <v>-0.05097312326227989</v>
       </c>
       <c r="AL3">
-        <v>130.1</v>
+        <v>3.03</v>
       </c>
       <c r="AM3">
-        <v>130.1</v>
+        <v>-23.57</v>
       </c>
       <c r="AN3">
-        <v>-5.435218203430124</v>
+        <v>-0.6482617586912065</v>
       </c>
       <c r="AO3">
-        <v>-4.570330514988471</v>
+        <v>-17.65676567656766</v>
       </c>
       <c r="AP3">
-        <v>-5.238240787909662</v>
+        <v>0.6748466257668712</v>
       </c>
       <c r="AQ3">
-        <v>-4.570330514988471</v>
+        <v>2.269834535426389</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PB Fintech Limited (NSEI:POLICYBZR)</t>
+          <t>Reliance Capital Limited (NSEI:RELCAPITAL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,23 +834,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0299</v>
+      </c>
       <c r="G4">
-        <v>-0.5010241704219582</v>
+        <v>-0.0780575710153175</v>
       </c>
       <c r="H4">
-        <v>-0.5010241704219582</v>
+        <v>-0.0780575710153175</v>
       </c>
       <c r="I4">
-        <v>-0.5456780008193363</v>
+        <v>-0.07502252572675108</v>
       </c>
       <c r="J4">
-        <v>-0.5456780008193363</v>
+        <v>-0.07502252572675108</v>
       </c>
       <c r="K4">
-        <v>-111.7</v>
+        <v>-165.1</v>
       </c>
       <c r="L4">
-        <v>-0.45759934453093</v>
+        <v>-0.07829468392848675</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,58 +877,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>349.5</v>
+        <v>113.4</v>
       </c>
       <c r="V4">
-        <v>0.1467316008228725</v>
+        <v>3.115384615384616</v>
+      </c>
+      <c r="W4">
+        <v>0.06585823128166261</v>
       </c>
       <c r="X4">
-        <v>0.09869082348314101</v>
+        <v>2.069064859395331</v>
+      </c>
+      <c r="Y4">
+        <v>-2.003206628113668</v>
       </c>
       <c r="AB4">
-        <v>0.09821698500217906</v>
+        <v>0.08642678056062233</v>
       </c>
       <c r="AD4">
-        <v>27.6</v>
+        <v>2118.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>27.6</v>
+        <v>2118.4</v>
       </c>
       <c r="AG4">
-        <v>-321.9</v>
+        <v>2005</v>
       </c>
       <c r="AH4">
-        <v>0.01145465864287197</v>
+        <v>0.9831074809727121</v>
       </c>
       <c r="AI4">
-        <v>0.04005224205485416</v>
+        <v>2.49811320754717</v>
       </c>
       <c r="AJ4">
-        <v>-0.1562621359223301</v>
+        <v>0.9821690996375037</v>
       </c>
       <c r="AK4">
-        <v>-0.9478798586572437</v>
+        <v>2.729376531445685</v>
       </c>
       <c r="AL4">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-10.61</v>
+        <v>-0.039</v>
       </c>
       <c r="AN4">
-        <v>-0.2123076923076923</v>
-      </c>
-      <c r="AO4">
-        <v>-63.73205741626794</v>
+        <v>-13.70245795601553</v>
       </c>
       <c r="AP4">
-        <v>2.476153846153846</v>
+        <v>-12.96895213454075</v>
       </c>
       <c r="AQ4">
-        <v>12.55419415645617</v>
+        <v>4056.410256410256</v>
       </c>
     </row>
   </sheetData>
